--- a/WorkBot/refactor-experimental/data/order_archive/Sysco/Sysco_Bakery_20251209.xlsx
+++ b/WorkBot/refactor-experimental/data/order_archive/Sysco/Sysco_Bakery_20251209.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,6 +506,321 @@
         <v>24.24</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5833462</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jalapenos (Sliced)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="E5" t="n">
+        <v>80.06999999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5204383</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pan Spray</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="E6" t="n">
+        <v>34.88</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2839082</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Flour - High Gluten</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="E7" t="n">
+        <v>849.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0017354</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hash Brown</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="E8" t="n">
+        <v>23.89</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2536555</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bacon (Pre-Cooked)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="E9" t="n">
+        <v>467.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1589290</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sausage - Patty (1.5oz)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="E10" t="n">
+        <v>121.45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2072536</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Frz Orange Juice</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>104.13</v>
+      </c>
+      <c r="E11" t="n">
+        <v>104.13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7468531</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Gatorade Cool Blue</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6297594</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Avocado - Halves Fresh</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>32.94</v>
+      </c>
+      <c r="E13" t="n">
+        <v>32.94</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4438911</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Grain Blend 5 Way</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>77.89</v>
+      </c>
+      <c r="E14" t="n">
+        <v>155.78</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1159946</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cheddar - Orange (Shredded)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="E15" t="n">
+        <v>113.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2366607</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Liquid Egg</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>43.51</v>
+      </c>
+      <c r="E16" t="n">
+        <v>174.04</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3716743</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Philadelphia Cream Cheese - Original</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>100.62</v>
+      </c>
+      <c r="E17" t="n">
+        <v>201.24</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1777309</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Liquid Egg Yolk</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>70.56999999999999</v>
+      </c>
+      <c r="E18" t="n">
+        <v>70.56999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6596787</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sweet Street - Bar Lemon Luscious Sliced</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>80.79000000000001</v>
+      </c>
+      <c r="E19" t="n">
+        <v>80.79000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
